--- a/frontend/public/templates/publications-import-template.xlsx
+++ b/frontend/public/templates/publications-import-template.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -487,21 +487,28 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>2. 必填：论文题目、作者、年份。系统优先按 DOI 更新已有论文；DOI 为空时按论文题目和年份匹配。</t>
+          <t>2. 只需要填写 GB/T 7714-2025 格式引文，系统会自动拆分作者、题目、期刊、年份、卷期页和 DOI。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>3. 可见范围可填写：公开、成员可见、管理员可见。</t>
+          <t>3. 摘要、可见范围、PDF附件、首页排序为管理字段；没有就留空。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>4. PDF 附件列只作提醒；批量导入先导入文字信息，PDF 请在单条论文编辑页面上传。</t>
+          <t>4. 首页排序：0 表示不在首页展示；大于 0 时按数字从小到大展示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5. PDF 附件列只作提醒；批量导入先导入文字信息，PDF 请在单条论文编辑页面上传。</t>
         </is>
       </c>
     </row>
@@ -516,113 +523,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="82" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>论文题目</t>
+          <t>GB/T 7714-2025格式引文</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>作者</t>
+          <t>摘要</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>期刊</t>
+          <t>可见范围</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>年份</t>
+          <t>PDF附件</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>DOI</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>可见范围</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>摘要</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>PDF附件</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>排序</t>
+          <t>首页排序</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>示例论文题目</t>
+          <t>作者1, 作者2. 示例论文题目. Environmental Research, 2026, 270: 121036. DOI: 10.0000/example</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>作者1; 作者2; 作者3</t>
+          <t>填写论文摘要。</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Environmental Research</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>10.0000/example</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
           <t>公开</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>填写论文摘要。</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>导入后在单条论文中上传 PDF</t>
         </is>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="E2" s="5" t="n">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"公开,成员可见,管理员可见"</formula1>
     </dataValidation>
   </dataValidations>
